--- a/diseases/d204/2026-2029.xlsx
+++ b/diseases/d204/2026-2029.xlsx
@@ -15447,118 +15447,517 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Japan NIID South American hemorrhagic fever notifications.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>D204</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>South American hemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>南美出血热</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="inlineStr">
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO78" t="inlineStr">
+      <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP78" t="inlineStr">
+      <c r="AP80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR78" t="inlineStr">
+      <c r="AR80" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS78" t="inlineStr"/>
-      <c r="AT78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV78" t="inlineStr">
+      <c r="AV80" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW78" t="inlineStr">
+      <c r="AW80" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
+      <c r="AX80" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY78" t="inlineStr">
+      <c r="AY80" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
+      <c r="AZ80" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA78" t="inlineStr">
+      <c r="BA80" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB78" t="inlineStr">
+      <c r="BB80" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC78" t="inlineStr">
+      <c r="BC80" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -15680,7 +16079,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -15690,7 +16089,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -15710,7 +16109,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d204/2026-2029.xlsx
+++ b/diseases/d204/2026-2029.xlsx
@@ -15963,6 +15963,405 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Japan NIID South American hemorrhagic fever notifications.</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN82" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15996,7 +16395,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16478,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -16089,7 +16488,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
@@ -16109,7 +16508,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d204/2026-2029.xlsx
+++ b/diseases/d204/2026-2029.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16357,6 +16357,405 @@
         </is>
       </c>
       <c r="BC82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Japan NIID South American hemorrhagic fever notifications.</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN84" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16395,7 +16794,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -16478,7 +16877,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -16488,7 +16887,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11">
@@ -16508,7 +16907,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d204/2026-2029.xlsx
+++ b/diseases/d204/2026-2029.xlsx
@@ -16761,6 +16761,550 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Japan NIID South American hemorrhagic fever notifications.</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16794,7 +17338,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -16877,7 +17421,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -16887,7 +17431,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -16907,7 +17451,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d204/2026-2029.xlsx
+++ b/diseases/d204/2026-2029.xlsx
@@ -17188,118 +17188,517 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Japan NIID South American hemorrhagic fever notifications.</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>D204</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>South American hemorrhagic fever</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
         <is>
           <t>南美出血热</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="inlineStr">
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO87" t="inlineStr">
+      <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP87" t="inlineStr">
+      <c r="AP89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR87" t="inlineStr">
+      <c r="AR89" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS87" t="inlineStr"/>
-      <c r="AT87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV87" t="inlineStr">
+      <c r="AV89" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW87" t="inlineStr">
+      <c r="AW89" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
+      <c r="AX89" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY87" t="inlineStr">
+      <c r="AY89" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
+      <c r="AZ89" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA87" t="inlineStr">
+      <c r="BA89" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB87" t="inlineStr">
+      <c r="BB89" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC87" t="inlineStr">
+      <c r="BC89" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -17421,7 +17820,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -17431,7 +17830,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -17451,7 +17850,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d204/2026-2029.xlsx
+++ b/diseases/d204/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2913,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4654,6 +4664,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6395,6 +6410,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8136,6 +8156,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10276,6 +10301,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12017,6 +12047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13758,6 +13793,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15898,6 +15938,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17637,6 +17682,11 @@
       <c r="S89" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">

--- a/diseases/d204/2026-2029.xlsx
+++ b/diseases/d204/2026-2029.xlsx
@@ -17754,6 +17754,405 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>south-american-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D204</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>南美出血热</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>South American hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Japan NIID South American hemorrhagic fever notifications.</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN91" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_JP_SOUTH_AMERICAN_HEMORRHAGIC_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17787,7 +18186,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17870,7 +18269,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -17880,7 +18279,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -17900,7 +18299,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
